--- a/products-storage/05-ks-bez-vozvrata/02-reestr-prilozheniy.xlsx
+++ b/products-storage/05-ks-bez-vozvrata/02-reestr-prilozheniy.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2">
-        <f>ЕСЛИ(F2="ОК";"✓";"✗")</f>
+        <f>IF(F2="ОК","✓","✗")</f>
         <v/>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3">
-        <f>ЕСЛИ(F3="ОК";"✓";"✗")</f>
+        <f>IF(F3="ОК","✓","✗")</f>
         <v/>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4">
-        <f>ЕСЛИ(F4="ОК";"✓";"✗")</f>
+        <f>IF(F4="ОК","✓","✗")</f>
         <v/>
       </c>
     </row>
